--- a/docs/OEM_Battery_Data_Request.xlsx
+++ b/docs/OEM_Battery_Data_Request.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Euler" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Mahindra" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Bajaj" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TVS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Piaggio" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -136,8 +138,13 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,11 +166,55 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -220,6 +271,14 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,7 +665,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PURPOSE: this workbook lists the battery data we need from each OEM to build accurate State-of-Health (SoH) and Remaining-Useful-Life (RUL) prediction models. One sheet per OEM (Euler · Mahindra · Bajaj). Each sheet shows the parameters we ask for, whether we get them today, the exact specification, why each matters, the data-quality problems to fix, and the sampling/coverage requirements.</t>
+          <t>PURPOSE: this workbook lists the battery data that would help us build accurate State-of-Health (SoH) and Remaining-Useful-Life (RUL) prediction models. One sheet per OEM. Each sheet shows the parameters we'd love to receive, whether we get them today, the exact specification, why each matters, a few notes on data quality, and the sampling/coverage that helps most.</t>
         </is>
       </c>
     </row>
@@ -633,14 +692,14 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   🔴 CRITICAL   = absolutely necessary; the model cannot be trusted without it.</t>
+          <t xml:space="preserve">   🔴 Essential   = the signals an accurate model really depends on — these matter most.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   🟡 Good-to-have = a few high-value extras; nice if cheap, skip if it needs new hardware.</t>
+          <t xml:space="preserve">   🟡 Good-to-have = a few high-value extras — nice to have if they're easy; no need to add hardware.</t>
         </is>
       </c>
     </row>
@@ -657,7 +716,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>PLEASE KEEP THE LIST TIGHT. We have deliberately asked for ~10 critical signals and ~3 extras — not a long wish-list. A focused, high-quality, high-resolution feed of these beats hundreds of random parameters.</t>
+          <t>We've kept this list short on purpose — about 10 key signals and a few extras, rather than a long wish-list. A focused, high-resolution feed of these is far more useful to us than hundreds of parameters.</t>
         </is>
       </c>
     </row>
@@ -667,14 +726,14 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>THREE THINGS THAT MATTER MORE THAN ANY SINGLE FIELD:</t>
+          <t>THREE THINGS THAT HELP THE MOST:</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1.  RESOLUTION — raw time-series during charging (≤60 s), not monthly aggregates. We need to see charge curves.</t>
+          <t xml:space="preserve">    1.  RESOLUTION — raw time-series during charging (≤60 s) rather than monthly aggregates, so we can see the charge curves.</t>
         </is>
       </c>
     </row>
@@ -688,7 +747,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3.  OLDEST VEHICLES — include the highest-km / oldest units; they are the only end-of-life examples there are.</t>
+          <t xml:space="preserve">    3.  OLDEST VEHICLES — wherever possible, include the highest-km / oldest units; they're the best end-of-life examples we can learn from.</t>
         </is>
       </c>
     </row>
@@ -750,7 +809,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>1 ·  PARAMETERS REQUESTED   (ask for these — and only these)</t>
+          <t>1 ·  Parameters we'd love to receive</t>
         </is>
       </c>
     </row>
@@ -897,7 +956,7 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -924,12 +983,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>❌ Broken</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Needs work</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -939,7 +998,7 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>THE model's training label. Today's value is unusable (section 2).</t>
+          <t>This is the model's training label; today's value isn't usable yet (see section 2).</t>
         </is>
       </c>
     </row>
@@ -978,7 +1037,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -988,7 +1047,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>km, cumulative, MONOTONIC (never resets/jumps). Today it is noisy.</t>
+          <t>km, cumulative and monotonic (ideally no resets/jumps). Today it's a little noisy.</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -1005,7 +1064,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1020,7 +1079,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Normalises SoH; we currently GUESS capacity from a variant map.</t>
+          <t>Normalises SoH; today we estimate capacity from a variant map.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1091,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -1111,7 +1170,7 @@
       <c r="C18" s="15" t="inlineStr"/>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>mΩ, if the BMS already estimates it (do NOT add new hardware for this).</t>
+          <t>mΩ, if the BMS already estimates it (only if your BMS already provides it — no new hardware needed).</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1121,53 +1180,77 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>2 ·  DATA-QUALITY PROBLEMS IN THE DATA WE GET TODAY   (please fix these)</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2 ·  Notes on today's data  ·  where the feed could be stronger</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>•  The 'batterySoh' field is GARBAGE — it contains impossible values (0 and &gt;70,000 for a 0–100% quantity). Unusable as-is.</t>
-        </is>
-      </c>
+          <t>•  The 'batterySoh' field isn't usable as-is — it carries out-of-range values (0 and &gt;70,000 for what should be a 0–100% quantity), so we can't treat it as a real SoH.</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="22" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>•  The SoH we derive from 'batteryRemainingCapacity' is artifact-laden: single-month drops of 14–25 pp (physically impossible for Li-ion — these are BMS capacity RE-ESTIMATION JUMPS), and values FROZEN for 11–18 months (stale/held). Root cause: LFP's flat voltage plateau makes the BMS recalibrate capacity in steps. ~32% of vehicles are affected.</t>
-        </is>
-      </c>
+          <t>•  The SoH we derive from 'batteryRemainingCapacity' shows artifacts — single-month drops of 14–25 pp that aren't physically realistic, which look like BMS re-estimation steps rather than true fade.</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="22" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>•  Data arrives as monthly aggregates — we cannot see individual charge curves, which is exactly what we need to compute a clean capacity.</t>
-        </is>
-      </c>
+          <t>•  Data arrives as monthly aggregates, so we can't see individual charge curves — which is what we need to read capacity.</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>•  Only an aggregate 'cellImbalance' is sent — no per-cell or min/max cell voltages.</t>
-        </is>
-      </c>
+          <t>•  Only an aggregate 'cellImbalance' is sent today — per-cell or min/max cell voltages would help a lot.</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>•  Odometer is noisy / non-monotonic, so distance-based remaining-life is unreliable.</t>
-        </is>
-      </c>
+          <t>•  The odometer is a little noisy / non-monotonic, which makes distance-based remaining-life hard to use.</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>•  Telemetry starts ~Oct 2023 and very few vehicles have reached end-of-life — almost no aged examples to learn from.</t>
-        </is>
-      </c>
+          <t>•  Telemetry starts ~Oct 2023 and few vehicles have reached end-of-life yet, so there are very few aged examples to learn from.</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="22" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -1179,9 +1262,13 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). NOT monthly or daily aggregates — we must see whole charge curves.</t>
-        </is>
-      </c>
+          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). rather than monthly or daily aggregates — we must see whole charge curves.</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="22" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
@@ -1189,13 +1276,21 @@
           <t>•  FULL CHARGES: at least weekly, capture one charge that reaches ~100% SoC end-to-end. This is the capacity/SoH anchor — and it is essential for LFP, whose mid-range voltage is almost flat (capacity is only readable near a full charge).</t>
         </is>
       </c>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="22" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>•  HISTORY &amp; FLEET: full history from commissioning, and you MUST include the OLDEST / highest-km vehicles. End-of-life examples are what our model lacks most — a fleet of only young vehicles cannot teach end-of-life.</t>
-        </is>
-      </c>
+          <t>•  HISTORY &amp; FLEET: full history from commissioning, and please include the oldest / highest-km vehicles where you can. End-of-life examples are what our model lacks most — a fleet of only young vehicles can't show end-of-life behaviour.</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
@@ -1203,6 +1298,10 @@
           <t>•  RAW VALUES: send the BMS's raw values, not smoothed / clamped / 'last-good' display values. Document units, sign convention, and any scaling for every signal.</t>
         </is>
       </c>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="22" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
@@ -1210,6 +1309,10 @@
           <t>•  IDENTIFIERS: every row keyed by VIN + timestamp. Provide a static per-VIN sheet: nameplate spec + commissioning date (see rows above).</t>
         </is>
       </c>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1268,7 +1371,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>1 ·  PARAMETERS REQUESTED   (ask for these — and only these)</t>
+          <t>1 ·  Parameters we'd love to receive</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1437,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -1349,7 +1452,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>THE blocker — with no current, NO SoH is possible for 98% of the fleet.</t>
+          <t>The main gap — without current, SoH can't be computed for ~98% of the fleet.</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1464,12 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1415,12 +1518,12 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -1442,12 +1545,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -1496,7 +1599,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -1523,7 +1626,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1550,7 +1653,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -1629,7 +1732,7 @@
       <c r="C18" s="15" t="inlineStr"/>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>mΩ, if the BMS already estimates it (do NOT add new hardware for this).</t>
+          <t>mΩ, if the BMS already estimates it (only if your BMS already provides it — no new hardware needed).</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1639,46 +1742,66 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>2 ·  DATA-QUALITY PROBLEMS IN THE DATA WE GET TODAY   (please fix these)</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2 ·  Notes on today's data  ·  where the feed could be stronger</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>•  ~98% of the fleet (the native feed) has NO current and NO voltage → SoH is impossible for them. Only ~233 of 11,187 are measurable.</t>
-        </is>
-      </c>
+          <t>•  About 98% of the fleet (the native feed) has no current and no voltage, so SoH can't be computed for them — only ~233 of 11,187 are measurable today.</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="22" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>•  The measurable (Intellicar) subset is sampled too sparsely (roughly monthly) to capture enough charge cycles for reliable coulomb counting.</t>
-        </is>
-      </c>
+          <t>•  The measurable (Intellicar) subset is sampled fairly sparsely (roughly monthly), which makes it hard to capture enough charge cycles for reliable coulomb counting.</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="22" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>•  The two feeds cover different time windows (current-feed from 2022, native feed only from Jan 2025), so early-life degradation was never recorded for most vehicles.</t>
-        </is>
-      </c>
+          <t>•  The two feeds cover different time windows (current-feed from 2022, native feed only from Jan 2025), so early-life degradation wasn't captured for most vehicles.</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>•  Odometer is logged late and sparsely → distance-based remaining-life is not usable.</t>
-        </is>
-      </c>
+          <t>•  The odometer is logged late and sparsely, so distance-based remaining-life isn't usable yet.</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>•  No voltage anywhere → no open-circuit-voltage / dV-dQ capacity cross-check is possible.</t>
-        </is>
-      </c>
+          <t>•  No voltage anywhere today, so an open-circuit-voltage / dV-dQ capacity cross-check isn't possible.</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1690,9 +1813,13 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). NOT monthly or daily aggregates — we must see whole charge curves.</t>
-        </is>
-      </c>
+          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). rather than monthly or daily aggregates — we must see whole charge curves.</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="22" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
@@ -1700,13 +1827,21 @@
           <t>•  FULL CHARGES: at least weekly, capture one charge that reaches ~100% SoC end-to-end. This is the capacity/SoH anchor — and it is essential for LFP, whose mid-range voltage is almost flat (capacity is only readable near a full charge).</t>
         </is>
       </c>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="22" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>•  HISTORY &amp; FLEET: full history from commissioning, and you MUST include the OLDEST / highest-km vehicles. End-of-life examples are what our model lacks most — a fleet of only young vehicles cannot teach end-of-life.</t>
-        </is>
-      </c>
+          <t>•  HISTORY &amp; FLEET: full history from commissioning, and please include the oldest / highest-km vehicles where you can. End-of-life examples are what our model lacks most — a fleet of only young vehicles can't show end-of-life behaviour.</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="22" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
@@ -1714,6 +1849,10 @@
           <t>•  RAW VALUES: send the BMS's raw values, not smoothed / clamped / 'last-good' display values. Document units, sign convention, and any scaling for every signal.</t>
         </is>
       </c>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
@@ -1721,6 +1860,10 @@
           <t>•  IDENTIFIERS: every row keyed by VIN + timestamp. Provide a static per-VIN sheet: nameplate spec + commissioning date (see rows above).</t>
         </is>
       </c>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1771,14 +1914,14 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>WHAT WE GET TODAY: the BMS's reported SoH % (which is relatively clean) plus SoC, temperature, odometer and cycle counts — but NO current and NO voltage. So we cannot verify or recompute the SoH; it is an unaudited black box, and the fleet is very young. This is a MISSING-SIGNALS ask. Chemistry is LFP.</t>
+          <t>WHAT WE GET TODAY: the BMS's reported SoH % (which is relatively clean) plus SoC, temperature, odometer and cycle counts — but no current and no voltage. So we can't independently verify or recompute the SoH, and the fleet is still very young. This is mainly a missing-signals ask. Chemistry is LFP.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>1 ·  PARAMETERS REQUESTED   (ask for these — and only these)</t>
+          <t>1 ·  Parameters we'd love to receive</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1987,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -1871,12 +2014,12 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1898,12 +2041,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -2006,7 +2149,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -2060,7 +2203,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -2087,7 +2230,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>🔴 CRITICAL</t>
+          <t>🔴 Essential</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -2166,7 +2309,7 @@
       <c r="C19" s="15" t="inlineStr"/>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>mΩ, if the BMS already estimates it (do NOT add new hardware for this).</t>
+          <t>mΩ, if the BMS already estimates it (only if your BMS already provides it — no new hardware needed).</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -2176,39 +2319,55 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>2 ·  DATA-QUALITY PROBLEMS IN THE DATA WE GET TODAY   (please fix these)</t>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>2 ·  Notes on today's data  ·  where the feed could be stronger</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>•  No current and no voltage at all → SoH cannot be validated or recomputed; we have no coulomb-counting or dV-dQ capability, and depend entirely on the BMS's reported SoH (a black box).</t>
-        </is>
-      </c>
+          <t>•  No current and no voltage today, so we can't independently validate or recompute SoH — we depend entirely on the reported value.</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="22" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>•  Because there is no independent signal, we cannot detect WHEN the reported SoH is wrong.</t>
-        </is>
-      </c>
+          <t>•  With no independent signal, we can't tell when the reported SoH drifts.</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>•  Telemetry only starts ~Sep 2025, so every vehicle is young — there are zero aged / end-of-life examples to learn from.</t>
-        </is>
-      </c>
+          <t>•  Telemetry only starts ~Sep 2025, so every vehicle is young — there are no aged / end-of-life examples to learn from yet.</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>•  No cell-level data, so weak-cell / imbalance degradation is invisible.</t>
-        </is>
-      </c>
+          <t>•  No cell-level data today, so early weak-cell / imbalance degradation isn't visible.</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -2220,9 +2379,13 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). NOT monthly or daily aggregates — we must see whole charge curves.</t>
-        </is>
-      </c>
+          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). rather than monthly or daily aggregates — we must see whole charge curves.</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="22" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
@@ -2230,13 +2393,21 @@
           <t>•  FULL CHARGES: at least weekly, capture one charge that reaches ~100% SoC end-to-end. This is the capacity/SoH anchor — and it is essential for LFP, whose mid-range voltage is almost flat (capacity is only readable near a full charge).</t>
         </is>
       </c>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="22" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>•  HISTORY &amp; FLEET: full history from commissioning, and you MUST include the OLDEST / highest-km vehicles. End-of-life examples are what our model lacks most — a fleet of only young vehicles cannot teach end-of-life.</t>
-        </is>
-      </c>
+          <t>•  HISTORY &amp; FLEET: full history from commissioning, and please include the oldest / highest-km vehicles where you can. End-of-life examples are what our model lacks most — a fleet of only young vehicles can't show end-of-life behaviour.</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="22" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
@@ -2244,6 +2415,10 @@
           <t>•  RAW VALUES: send the BMS's raw values, not smoothed / clamped / 'last-good' display values. Document units, sign convention, and any scaling for every signal.</t>
         </is>
       </c>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
@@ -2251,6 +2426,10 @@
           <t>•  IDENTIFIERS: every row keyed by VIN + timestamp. Provide a static per-VIN sheet: nameplate spec + commissioning date (see rows above).</t>
         </is>
       </c>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2271,4 +2450,1132 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E86C1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>TVS — Battery Telemetry Data Request  (Turno SoH / RUL prediction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WE GET TODAY: we can't see TVS battery telemetry in S3 yet. There is no TVS native feed, and no TVS VINs (WMI 'MD6…') appear in the shared 'intellicar' feed across 2022–2026 — only a single TVS unit (King) shows up in our resale records. This sheet is our request to start the feed; please confirm the VIN range / WMI so we can locate any data that already exists. All packs are LFP. Variant in our records: TVS King.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>1 ·  Parameters we'd love to receive  (a fresh feed for the entire fleet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Do we get it now?</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Required specification (units · resolution · convention)</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Why we need it — what it unlocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>ISO-8601 with timezone, one per reading.</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Anchors every signal in time; lets us segment charge vs drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Battery current</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Amps, SIGNED (please state the sign convention). ≤60 s during charge.</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Capacity from charge segments (coulomb counting); C-rate stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Battery voltage (pack)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Volts, pack level, ≤60 s during charge.</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Full-charge detection; voltage-based capacity checks (dV/dQ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>State of Charge (SoC)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>%, 0–100, BMS value.</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Segment by ΔSoC; capacity = charge-Ah ÷ ΔSoC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Battery temperature</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>°C — pack MIN and MAX (per-module if available).</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Primary degradation driver; needed to temp-correct capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Full-charge capacity / SoH</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>BMS pack capacity (Ah) AND SoH %, captured at ≥95% SoC, RAW value.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>The model's training label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Operating state</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Enum: charging / driving / idle.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Segmentation of charge vs drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Odometer</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>km, cumulative and monotonic (ideally no resets/jumps), logged from day one.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Remaining-life in km.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Nameplate spec (per model)</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Per variant (TVS King) — all LFP: rated capacity (Ah &amp; kWh), nominal pack voltage, cell layout (series×parallel).</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Normalises SoH across variants; confirms pack capacity per model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Commissioning date (per VIN)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Date of first use / sale, per VIN.</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Anchors battery age.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Per-cell (or min &amp; max cell) voltage</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Good-to-have</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>mV per cell, or pack min-cell &amp; max-cell voltage + cell-imbalance, time-stamped.</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Weak/aging cells show up here first; also a safety signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Cumulative Ah throughput + equivalent full cycles</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Good-to-have</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Lifetime charge &amp; discharge Ah (BMS counter), and BMS equivalent-full-cycle count.</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Drift-free usage/aging driver — better than us integrating noisy current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Internal resistance / DC-IR estimate</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Good-to-have</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>mΩ, only if your BMS already provides it — no new hardware needed.</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Direct power-fade / SoH signal, complementary to capacity fade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2 ·  Setting the feed up well  ·  a few pitfalls worth avoiding from day one</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>•  Sending raw BMS values (not smoothed / clamped / 'last-good' display values) keeps real capacity steps visible — smoothing can make SoH look artificially stable.</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>•  On LFP, capacity is only readable near a full charge (the mid-range voltage is almost flat), so capturing full charges end-to-end matters most (see section 3).</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>•  A monotonic odometer, logged from day one, keeps distance-based remaining-life usable — late or resetting odometers are hard to work with.</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>•  Per-cell (or min/max cell) voltage is the earliest sign of a weak cell; an aggregate-only value tends to hide it.</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>•  As the fleet ages, including the oldest / highest-km vehicles helps a lot — end-of-life examples are the hardest data to get and the most valuable.</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>•  Telemetry starts ~Oct 2023 and few vehicles have reached end-of-life yet, so there are very few aged examples to learn from.</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>3 ·  SAMPLING &amp; COVERAGE   (applies to every parameter above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). rather than monthly or daily aggregates — we must see whole charge curves.</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>•  FULL CHARGES: at least weekly, capture one charge that reaches ~100% SoC end-to-end. This is the capacity/SoH anchor — and it is essential for LFP, whose mid-range voltage is almost flat (capacity is only readable near a full charge).</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>•  HISTORY &amp; FLEET: full history from commissioning, and please include the oldest / highest-km vehicles where you can. End-of-life examples are what our model lacks most — a fleet of only young vehicles can't show end-of-life behaviour.</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>•  RAW VALUES: send the BMS's raw values, not smoothed / clamped / 'last-good' display values. Document units, sign convention, and any scaling for every signal.</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>•  IDENTIFIERS: every row keyed by VIN + timestamp. Provide a static per-VIN sheet: nameplate spec + commissioning date (see rows above).</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008E44AD"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>PIAGGIO — Battery Telemetry Data Request  (Turno SoH / RUL prediction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WE GET TODAY: two feeds. The native Piaggio feed (from Aug 2023) carries signed discharge-current, SoC, odometer and a charging flag. The shared 'intellicar' feed (from 2022) adds pack voltage, signed current, SoC, charge-cycle count and odometer for a large share of the fleet — so SoH IS measurable for Piaggio (coulomb counting and dV/dQ). Piaggio is the 2nd-largest OEM in the intellicar feed. Main gaps: no direct battery temperature and no BMS-reported SoH. All packs are LFP. Variants: Ape E-City FX NE Max · Ape E-Xtra FX · Ape E-Xtra FX Max.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>1 ·  Parameters we'd love to receive  (two feeds today — see notes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Do we get it now?</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Required specification (units · resolution · convention)</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Why we need it — what it unlocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>✅ Yes</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>ISO-8601 with timezone, one per reading.</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Anchors every signal in time; lets us segment charge vs drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Battery current</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>✅ Yes</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Amps, SIGNED. Present in the intellicar feed; the native feed sends 'batteryDischargeCurrent' (please confirm charge-current sign). ≤60 s during charge.</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Capacity from charge segments (coulomb counting); C-rate stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Battery voltage (pack)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Partial</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Volts, pack level. Today only in the intellicar feed (~78% of rows) — please add it to the native feed too. ≤60 s during charge.</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Full-charge detection; voltage-based capacity checks (dV/dQ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>State of Charge (SoC)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>✅ Yes</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>%, 0–100, BMS value.</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Segment by ΔSoC; capacity = charge-Ah ÷ ΔSoC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Battery temperature</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Needs work</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>°C — pack/battery MIN and MAX. Today we only get controller &amp; motor temperature, not battery-pack temperature.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Primary degradation driver; needed to temp-correct capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Full-charge capacity / SoH</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>BMS pack capacity (Ah) AND SoH % at ≥95% SoC, RAW. No reported SoH today — we derive it from current + SoC / voltage.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>The model's training label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Operating state</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>✅ Yes</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Enum: charging / driving / idle. A 'batteryCharging' flag is present today.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Segmentation of charge vs drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Odometer</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>✅ Yes</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>km, cumulative and monotonic (ideally no resets/jumps), logged from day one.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Remaining-life in km.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Nameplate spec (per model)</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Partial</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Per variant (Ape E-City FX NE Max / Ape E-Xtra FX / Ape E-Xtra FX Max) — all LFP: rated capacity (Ah &amp; kWh), nominal pack voltage, cell layout (series×parallel).</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Normalises SoH across variants; confirms pack capacity per model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Commissioning date (per VIN)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>🔴 Essential</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Partial</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Date of first use / sale, per VIN.</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Anchors battery age.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Per-cell (or min &amp; max cell) voltage</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Good-to-have</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>mV per cell, or pack min-cell &amp; max-cell voltage + cell-imbalance, time-stamped.</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Weak/aging cells show up here first; also a safety signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Cumulative Ah throughput + equivalent full cycles</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Good-to-have</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Partial</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Lifetime charge &amp; discharge Ah and equivalent-full-cycle count. A per-charge 'chargeCycle' count is already in the intellicar feed.</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Drift-free usage/aging driver — better than us integrating noisy current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Internal resistance / DC-IR estimate</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Good-to-have</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>mΩ, only if your BMS already provides it — no new hardware needed.</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Direct power-fade / SoH signal, complementary to capacity fade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2 ·  Notes on today's data  ·  where the feed could be stronger</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>•  Two feeds carry Piaggio: the native feed (from Aug 2023) has discharge-current + SoC + odometer + a charging flag; the shared 'intellicar' feed (from 2022) adds pack voltage, signed current, SoC, charge-cycle count and odometer for a large share of the fleet — so SoH is measurable.</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>•  No direct battery/pack temperature in either feed today — only controller and motor temperature. Since heat is the biggest ageing factor for LFP, a pack-temperature reading would help the most.</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>•  No BMS-reported SoH or full-charge capacity — we derive SoH from current + SoC (coulomb) and voltage (dV/dQ). A raw capacity/SoH at a full charge would anchor and validate it.</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>•  Pack voltage is only in the intellicar feed (~78% of rows) and missing from the native feed — having it on the main feed would let us validate every vehicle.</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>•  The native current channel is labelled 'batteryDischargeCurrent' — please confirm charge current (and its sign) is captured during charging, so charge-segment coulomb counting works.</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>•  Telemetry starts ~Oct 2023 and few vehicles have reached end-of-life yet, so there are very few aged examples to learn from.</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>3 ·  SAMPLING &amp; COVERAGE   (applies to every parameter above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>•  RESOLUTION: raw time-series at ≤60 s (ideally 10 s) DURING CHARGING; driving can be coarser (≤300 s). rather than monthly or daily aggregates — we must see whole charge curves.</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>•  FULL CHARGES: at least weekly, capture one charge that reaches ~100% SoC end-to-end. This is the capacity/SoH anchor — and it is essential for LFP, whose mid-range voltage is almost flat (capacity is only readable near a full charge).</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>•  HISTORY &amp; FLEET: full history from commissioning, and please include the oldest / highest-km vehicles where you can. End-of-life examples are what our model lacks most — a fleet of only young vehicles can't show end-of-life behaviour.</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>•  RAW VALUES: send the BMS's raw values, not smoothed / clamped / 'last-good' display values. Document units, sign convention, and any scaling for every signal.</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>•  IDENTIFIERS: every row keyed by VIN + timestamp. Provide a static per-VIN sheet: nameplate spec + commissioning date (see rows above).</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>